--- a/config/new-five-tables/source/05_TCIM_十题_综合判断记忆写入与TEVV表_V0.2.1_唯一运行版.xlsx
+++ b/config/new-five-tables/source/05_TCIM_十题_综合判断记忆写入与TEVV表_V0.2.1_唯一运行版.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Ref3da7627a6d4000"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUNTIME_CONTRACT" sheetId="2" r:id="R374d01e9572e480f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTION_INDEX" sheetId="3" r:id="Rabd3816b93a64363"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA" sheetId="4" r:id="R4fdc646565b048b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICTIONARY" sheetId="5" r:id="R192693241b3b411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENUMS" sheetId="6" r:id="Rcc4511473ca44180"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_SUMMARY" sheetId="7" r:id="R84f7bc157e8e46a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHANGELOG" sheetId="8" r:id="R3425ebb3ec984ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R2b79c8c878e54c2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUNTIME_CONTRACT" sheetId="2" r:id="R6944a035a6af4b2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTION_INDEX" sheetId="3" r:id="R40c9fabf51cf4074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA" sheetId="4" r:id="Rdc611ffc6844402f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICTIONARY" sheetId="5" r:id="Rfd0faff80a114569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENUMS" sheetId="6" r:id="R770612ab2cd04c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_SUMMARY" sheetId="7" r:id="R48501831568a4c0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHANGELOG" sheetId="8" r:id="Rde456a7378fb4c2e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9366,7 +9366,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1234c7eefa24519"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R021b9356e90b45fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
